--- a/FP224_result.xlsx
+++ b/FP224_result.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put cellphone and keychain in the drawer</t>
+          <t>Turn off the FloorLamp and put newspaper into the drawer</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -510,7 +510,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,159 +518,31 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>FAILED (Execution Errors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Put keychain and creditcard in the drawer and put keychain on the chair</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C3" t="n">
-        <v>50</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>95</v>
-      </c>
-      <c r="F3" t="n">
-        <v>90</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>FAILED (Execution Errors)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>FAILED (Execution Errors)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Put the laptop on the sofa</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>100</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Turn off the FloorLamp and put newspaper into the drawer</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>50</v>
-      </c>
-      <c r="C5" t="n">
-        <v>50</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="F4" s="2" t="n">
         <v>80</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>FAILED (Execution Errors)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Turn on the Television and open the book</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>100</v>
-      </c>
-      <c r="C6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>평균</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>89.56</v>
       </c>
     </row>
   </sheetData>

--- a/FP224_result.xlsx
+++ b/FP224_result.xlsx
@@ -494,7 +494,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turn off the FloorLamp and put newspaper into the drawer</t>
+          <t>Put cellphone and keychain in the drawer</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -510,7 +510,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>77.78</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>80</v>
+        <v>77.78</v>
       </c>
     </row>
   </sheetData>
